--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575528644</v>
+        <v>46157.93119852506</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93119852506</v>
+        <v>46157.93185830715</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93185830715</v>
+        <v>46157.93406910128</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406910128</v>
+        <v>46157.93725016708</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93725016708</v>
+        <v>46158.28222580933</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28222580933</v>
+        <v>46158.29709759546</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29709759546</v>
+        <v>46158.29822577021</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29822577021</v>
+        <v>46158.33393530422</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33393530422</v>
+        <v>46158.3686330565</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3686330565</v>
+        <v>46158.37294288541</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
